--- a/tables/Table S4.xlsx
+++ b/tables/Table S4.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="11.6640625" customWidth="1" style="9" min="1" max="1"/>
@@ -647,263 +647,299 @@
           <t>Hazard Ratio (Survivorship)</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Emerald Reef</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+        <v>-0.544</v>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
+        <v>-0.048</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs Emerald Reef</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+        <v>-1.406</v>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0.016</v>
+        <v>-1.777</v>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>0.076*</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>MacArthur North (Urban) vs Emerald Reef</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0.004</v>
+        <v>-2.563</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0.0104</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0.011</v>
+        <v>-2.139</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0.0324</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Acidified + Bleaching vs Contemporary pH + Bleaching</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>ns</t>
+        <v>1.769</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>0.077*</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
+        <v>-0.744</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Tukey's (Growth Rate)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Urban vs Reef (Star Island, MacArthur North vs Emerald, Rainbow)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>-2.151</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-2.612</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Tukey's (Growth Rate; S. siderea Contemporary pH)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Emerald Reef vs Rainbow Reef</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
-        <v>1.042</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>*no model factors significant</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>-0.431</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Emerald Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
-        <v>1.757</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="n">
+        <v>2.144</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>-0.851</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Emerald Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
-        <v>3.475</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="F9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="n">
+        <v>3.808</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>-4.136</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.0016</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Rainbow Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>0.080*</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-3.712</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.0047</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n">
-        <v>1.644</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Daytime Calcification)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Emerald Reef vs Rainbow Reef</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>*no model factors significant</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="26" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
+      <c r="C13" s="8" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-3.299</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0.013</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs Star Island (Urban)</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="26" t="n">
-        <v>-1.493</v>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
+          <t>Urban vs Reef</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>-3.344</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>3.243</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.0031</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Tukey's (Growth Rate, S. siderea Acidified)</t>
+        </is>
+      </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="26" t="n">
-        <v>-3.398</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>0.0174</v>
+          <t>Emerald Reef vs Rainbow Reef</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>*no pH × site interaction (values above apply to both pH treatments)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Rainbow Reef vs Star Island (Urban)</t>
-        </is>
-      </c>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="26" t="n">
-        <v>-1.832</v>
+          <t>Emerald Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -914,28 +950,26 @@
     <row r="17">
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Rainbow Reef vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="26" t="n">
-        <v>-3.737</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>0.008699999999999999</v>
+          <t>Emerald Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>-0.862</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Star Island (Urban) vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="26" t="n">
-        <v>-1.905</v>
+          <t>Rainbow Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
@@ -944,24 +978,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Nighttime Calcification)</t>
-        </is>
-      </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs Rainbow Reef</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>*no model factors significant</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="26" t="n">
-        <v>0.095</v>
+          <t>Rainbow Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-0.862</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
@@ -972,13 +995,11 @@
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs Star Island (Urban)</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="26" t="n">
-        <v>-0.979</v>
+          <t>Star Island (Urban) vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.852</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
@@ -989,30 +1010,36 @@
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="26" t="n">
-        <v>-2.697</v>
+          <t>Urban vs Reef</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.617</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>0.068*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
     <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Tukey's (Daytime Calcification)</t>
+        </is>
+      </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Rainbow Reef vs Star Island (Urban)</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="26" t="n">
-        <v>-1.074</v>
+          <t>Emerald Reef vs Rainbow Reef</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>*site not significant</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.339</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
@@ -1023,56 +1050,39 @@
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Rainbow Reef vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="26" t="n">
-        <v>-2.791</v>
+          <t>Emerald Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-1.493</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>0.057*</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Star Island (Urban) vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="26" t="n">
-        <v>-1.718</v>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
+          <t>Emerald Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-3.398</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.017</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Day-Averaged Calcification)</t>
-        </is>
-      </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs Rainbow Reef</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>*no model factors significant</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="26" t="n">
-        <v>0.268</v>
+          <t>Rainbow Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-1.832</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
@@ -1083,100 +1093,305 @@
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs Star Island (Urban)</t>
-        </is>
-      </c>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="26" t="n">
-        <v>-1.436</v>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
+          <t>Rainbow Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-3.737</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Emerald Reef vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="26" t="n">
-        <v>-3.481</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>0.0147</v>
+          <t>Star Island (Urban) vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>-1.905</v>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Rainbow Reef vs Star Island (Urban)</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="26" t="n">
-        <v>-1.704</v>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
+          <t>Urban vs Reef</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>3.698</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Tukey's (Nighttime Calcification)</t>
+        </is>
+      </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Rainbow Reef vs MacArthur North (Urban)</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="26" t="n">
-        <v>-3.749</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>0.008500000000000001</v>
+          <t>Emerald Reef vs Rainbow Reef</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>*site not significant</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Emerald Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-0.979</v>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Emerald Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-2.697</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>0.068*</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1" s="9">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Rainbow Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-1.074</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Rainbow Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>-2.791</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>0.057*</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>Star Island (Urban) vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="30" t="n">
+      <c r="E34" s="8" t="n">
+        <v>-1.718</v>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Urban vs Reef</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>-1.261</v>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>2.666</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Tukey's (Day-Averaged Calcification)</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Emerald Reef vs Rainbow Reef</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>*site not significant</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Emerald Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-1.436</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Emerald Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-3.481</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Rainbow Reef vs Star Island (Urban)</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-1.704</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Rainbow Reef vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-3.749</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+    </row>
+    <row r="41" ht="39" customHeight="1" s="9">
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Star Island (Urban) vs MacArthur North (Urban)</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>-2.045</v>
       </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1" s="9"/>
-    <row r="41" ht="39" customHeight="1" s="9"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Urban vs Reef</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>-0.899</v>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0.0021</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A13:A18"/>
+  <mergeCells count="14">
+    <mergeCell ref="C29:D34"/>
+    <mergeCell ref="A8:A14"/>
+    <mergeCell ref="C22:D27"/>
+    <mergeCell ref="A36:A42"/>
+    <mergeCell ref="A22:A28"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="C15:D21"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A7:A12"/>
-    <mergeCell ref="A25:A30"/>
-    <mergeCell ref="E7:E12"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="A29:A35"/>
+    <mergeCell ref="C36:D41"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A15:A21"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tables/Table S4.xlsx
+++ b/tables/Table S4.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="11.6640625" customWidth="1" style="9" min="1" max="1"/>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" s="9">
       <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Urban vs Reef</t>
@@ -1377,20 +1377,118 @@
         <v>0.0021</v>
       </c>
     </row>
+    <row r="43" s="9">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Urban vs Reef (Oxygen Flux)</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Net Photosynthesis</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" s="9">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Respiration</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>0.065*</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" s="9">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Gross Photosynthesis</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" s="9">
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Photosynthesis:Respiration</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>-1.293</v>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="C29:D34"/>
-    <mergeCell ref="A8:A14"/>
-    <mergeCell ref="C22:D27"/>
-    <mergeCell ref="A36:A42"/>
     <mergeCell ref="A22:A28"/>
     <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A43:A46"/>
     <mergeCell ref="C15:D21"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A29:A35"/>
     <mergeCell ref="C36:D41"/>
+    <mergeCell ref="A8:A14"/>
+    <mergeCell ref="C22:D27"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A36:A42"/>
     <mergeCell ref="A15:A21"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/tables/Table S4.xlsx
+++ b/tables/Table S4.xlsx
@@ -3,22 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6380" yWindow="3380" windowWidth="26840" windowHeight="15680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3400" yWindow="2880" windowWidth="26840" windowHeight="15680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <name val="Aptos Narrow"/>
@@ -43,11 +40,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Times New Roman"/>
       <family val="1"/>
       <color theme="1"/>
@@ -56,15 +48,19 @@
     <font>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <sz val="9"/>
-      <scheme val="minor"/>
+      <vertAlign val="subscript"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,10 +71,50 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -92,100 +128,51 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -584,912 +571,1064 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="11.6640625" customWidth="1" style="9" min="1" max="1"/>
-    <col width="58.5" bestFit="1" customWidth="1" style="9" min="2" max="2"/>
-    <col width="8" customWidth="1" style="9" min="3" max="3"/>
-    <col width="5.6640625" bestFit="1" customWidth="1" style="9" min="4" max="4"/>
-    <col width="8.5" customWidth="1" style="9" min="5" max="5"/>
-    <col width="5.6640625" bestFit="1" customWidth="1" style="9" min="6" max="6"/>
+    <col width="11" customWidth="1" style="6" min="1" max="1"/>
+    <col width="35" customWidth="1" style="6" min="2" max="2"/>
+    <col width="8" customWidth="1" style="6" min="3" max="3"/>
+    <col width="5.6640625" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="8.5" customWidth="1" style="6" min="5" max="5"/>
+    <col width="5.6640625" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Response (Test)</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Comparison</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Orbicella faveolata</t>
         </is>
       </c>
-      <c r="D1" s="25" t="n"/>
+      <c r="D1" s="12" t="n"/>
       <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Siderastrea siderea</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="26" customHeight="1" s="9">
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="F1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" s="6">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Test Statistic</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Test Statistic</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Hazard Ratio (Survivorship)</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Survivorship (Cox Hazard Ratios)</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Emerald Reef</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="2" t="n">
         <v>-0.544</v>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="n">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>-0.048</v>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs Emerald Reef</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="2" t="n">
         <v>-1.406</v>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="n">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>-1.777</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>0.076*</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>MacArthur North (Urban) vs Emerald Reef</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="2" t="n">
         <v>-2.563</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.0104</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="2" t="n">
         <v>-2.139</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="3" t="n">
         <v>0.0324</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Acidified + Bleaching vs Contemporary pH + Bleaching</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="2" t="n">
         <v>1.769</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>0.077*</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="2" t="n">
         <v>-0.744</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Urban vs Reef (Star Island, MacArthur North vs Emerald, Rainbow)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Urban vs Reef</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>-2.151</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.031</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="2" t="n">
         <v>-2.612</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="3" t="n">
         <v>0.008999999999999999</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Growth Rate; S. siderea Contemporary pH)</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+    <row r="8" ht="20" customHeight="1" s="6">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Time-Averaged </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>V</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <sz val="9"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>M</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve"> (Urban vs Reef)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Heat</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="6">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Heat Stress</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4.188</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Growth Rate, Contemporary pH (Tukey's)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Rainbow Reef</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C10" s="2" t="n">
         <v>1.041</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>-0.431</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C11" s="2" t="n">
         <v>2.144</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>-0.851</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="8" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C12" s="2" t="n">
         <v>3.808</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.008</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E12" s="2" t="n">
         <v>-4.136</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F12" s="3" t="n">
         <v>0.0016</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="8" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C13" s="2" t="n">
         <v>1.04</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>-0.42</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="8" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C14" s="2" t="n">
         <v>2.591</v>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>0.080*</t>
         </is>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E14" s="2" t="n">
         <v>-3.712</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F14" s="3" t="n">
         <v>0.0047</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="8" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C15" s="2" t="n">
         <v>1.553</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>-3.299</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F15" s="3" t="n">
         <v>0.013</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Urban vs Reef</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C16" s="2" t="n">
         <v>-3.344</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.004</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E16" s="2" t="n">
         <v>3.243</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F16" s="3" t="n">
         <v>0.0031</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Growth Rate, S. siderea Acidified)</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Growth Rate, Acidified (Tukey's)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Rainbow Reef</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>*no pH × site interaction (values above apply to both pH treatments)</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*no pH × site interaction </t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="2" t="n">
         <v>-0.011</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="8" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="2" t="n">
         <v>-0.862</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="2" t="n">
         <v>-0.011</v>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="2" t="n">
         <v>-0.862</v>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="2" t="n">
         <v>-0.852</v>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Urban vs Reef</t>
         </is>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="2" t="n">
         <v>0.617</v>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Daytime Calcification)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Daytime Calcification (Tukey's)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Rainbow Reef</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>*site not significant</t>
         </is>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="2" t="n">
         <v>0.339</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="2" t="n">
         <v>-1.493</v>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="8" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="2" t="n">
         <v>-3.398</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F26" s="3" t="n">
         <v>0.017</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="8" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="2" t="n">
         <v>-1.832</v>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="8" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="2" t="n">
         <v>-3.737</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F28" s="3" t="n">
         <v>0.008699999999999999</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="8" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="2" t="n">
         <v>-1.905</v>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Urban vs Reef</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C30" s="2" t="n">
         <v>-0.51</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
         <v>3.698</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F30" s="3" t="n">
         <v>0.002</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Nighttime Calcification)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Nighttime Calcification (Tukey's)</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Rainbow Reef</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>*site not significant</t>
         </is>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="2" t="n">
         <v>0.095</v>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="2" t="n">
         <v>-0.979</v>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="8" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="2" t="n">
         <v>-2.697</v>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>0.068*</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1" s="9">
-      <c r="B32" s="8" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="2" t="n">
         <v>-1.074</v>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="8" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="2" t="n">
         <v>-2.791</v>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>0.057*</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="8" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="2" t="n">
         <v>-1.718</v>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="8" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Urban vs Reef</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C37" s="2" t="n">
         <v>-1.261</v>
       </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
         <v>2.666</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F37" s="3" t="n">
         <v>0.017</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Tukey's (Day-Averaged Calcification)</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Day-Averaged Calcification (Tukey's)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Rainbow Reef</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>*site not significant</t>
         </is>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="2" t="n">
         <v>0.268</v>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="8" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="2" t="n">
         <v>-1.436</v>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="8" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Emerald Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="2" t="n">
         <v>-3.481</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F40" s="3" t="n">
         <v>0.015</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="8" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs Star Island (Urban)</t>
         </is>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="2" t="n">
         <v>-1.704</v>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="8" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Rainbow Reef vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="2" t="n">
         <v>-3.749</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F42" s="3" t="n">
         <v>0.008500000000000001</v>
       </c>
     </row>
-    <row r="41" ht="39" customHeight="1" s="9">
-      <c r="B41" s="8" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Star Island (Urban) vs MacArthur North (Urban)</t>
         </is>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="2" t="n">
         <v>-2.045</v>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" s="9">
-      <c r="B42" s="8" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Urban vs Reef</t>
         </is>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C44" s="2" t="n">
         <v>-0.899</v>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
         <v>3.667</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F44" s="3" t="n">
         <v>0.0021</v>
       </c>
     </row>
-    <row r="43" s="9">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Urban vs Reef (Oxygen Flux)</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Oxygen Flux (Urban vs Reef)</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Net Photosynthesis</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C45" s="2" t="n">
         <v>0.631</v>
       </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="n">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
         <v>0.434</v>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" s="9">
-      <c r="B44" s="8" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Respiration</t>
         </is>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C46" s="2" t="n">
         <v>-0.92</v>
       </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="n">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
         <v>1.985</v>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>0.065*</t>
         </is>
       </c>
     </row>
-    <row r="45" s="9">
-      <c r="B45" s="8" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Gross Photosynthesis</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C47" s="2" t="n">
         <v>0.312</v>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="n">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
         <v>0.601</v>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" s="9">
-      <c r="B46" s="8" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Photosynthesis:Respiration</t>
         </is>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C48" s="2" t="n">
         <v>0.639</v>
       </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="n">
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
         <v>-1.293</v>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="C29:D34"/>
-    <mergeCell ref="A22:A28"/>
+  <mergeCells count="16">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C24:D29"/>
+    <mergeCell ref="C38:D43"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C15:D21"/>
+    <mergeCell ref="C17:D23"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A29:A35"/>
-    <mergeCell ref="C36:D41"/>
-    <mergeCell ref="A8:A14"/>
-    <mergeCell ref="C22:D27"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A3:A7"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A36:A42"/>
-    <mergeCell ref="A15:A21"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="C31:D36"/>
+    <mergeCell ref="A31:A37"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
